--- a/3_PPTurnover/input/dict/Dict_CCS_MoreEnergyConsumption.xlsx
+++ b/3_PPTurnover/input/dict/Dict_CCS_MoreEnergyConsumption.xlsx
@@ -5,15 +5,16 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\92978\Desktop\Unit-level-Turnover-Model-main\3_PPTurnover\input\dict\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\92978\Desktop\Unit-level-Turnover-Model\3_PPTurnover\input\dict\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D592F5D-A008-4106-B88B-C67C9EB3C47B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D42584C-64E6-4496-ADF8-440D1DD3A970}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="23236" windowHeight="13875" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="23236" windowHeight="13875" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="2" r:id="rId1"/>
+    <sheet name="Setting" sheetId="2" r:id="rId1"/>
+    <sheet name="Readme" sheetId="3" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -31,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
   <si>
     <t>Sector</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -42,6 +43,18 @@
   </si>
   <si>
     <t>Coal</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Unit</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>%</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>This file defines the increase in energy consumption associated with CCUS deployment.</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -49,7 +62,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -64,6 +77,12 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -73,7 +92,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -81,12 +100,29 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -102,10 +138,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -395,25 +427,33 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2D32436F-E862-4C65-950E-61559264FC99}">
-  <dimension ref="A1:B2"/>
+  <dimension ref="A1:C2"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="14.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.33203125" customWidth="1"/>
+    <col min="3" max="3" width="14.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
+    <row r="1" spans="1:3" ht="13.9" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+    <row r="2" spans="1:3" ht="13.9" x14ac:dyDescent="0.35">
+      <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B2">
+      <c r="B2" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2" s="1">
         <v>15</v>
       </c>
     </row>
@@ -422,4 +462,20 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CE7C7B71-AB74-4FD4-A53F-BAF4E91D59CB}">
+  <dimension ref="A4"/>
+  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="4" spans="1:1" ht="13.9" x14ac:dyDescent="0.35">
+      <c r="A4" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>